--- a/RDSML-Day-22 👉 Central Limit Theorem Using R/Normal distribution.xlsx
+++ b/RDSML-Day-22 👉 Central Limit Theorem Using R/Normal distribution.xlsx
@@ -1,30 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Programming/Github/R-for-Data-Science-and-Machine-Learning-with-NBICT-LAB-Batch-8/RDSML-Day-22 👉 Central Limit Theorem Using R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B88806-5A2B-1C4C-9AFC-409600048060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444F3809-7A02-2247-A485-1DBF0572CCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{1EA16512-5E89-ED4D-BB6D-D051CF46B8FE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1EA16512-5E89-ED4D-BB6D-D051CF46B8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$2:$B$172</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$2:$B$176</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$2:$B$177</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$2:$B$56</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$2:$B$172</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$2:$B$177</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$2:$B$56</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$2:$B$172</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$B$2:$B$177</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$B$2:$B$56</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$2:$B$176</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$2:$B$177</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$2:$B$176</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$2:$B$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,21 +44,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Normal distribution
 or 
 Gausian distribution</t>
+  </si>
+  <si>
+    <t>from 30 - 40</t>
+  </si>
+  <si>
+    <t>from 20 - 30</t>
+  </si>
+  <si>
+    <t>from 10 - 20</t>
+  </si>
+  <si>
+    <t>from 1 - 10</t>
+  </si>
+  <si>
+    <t>from 50 - 60</t>
+  </si>
+  <si>
+    <t>from 60 - 70</t>
+  </si>
+  <si>
+    <t>from 70 - 80</t>
+  </si>
+  <si>
+    <t>from 40 -50</t>
+  </si>
+  <si>
+    <t>from 80 - 90</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
@@ -86,13 +122,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -116,25 +161,27 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Chart Title</cx:v>
-        </cx:txData>
-      </cx:tx>
-    </cx:title>
+    <cx:title pos="t" align="ctr" overlay="0"/>
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="clusteredColumn" uniqueId="{06CD7054-E9FD-A441-85AB-F3DD861FE591}">
+          <cx:dataPt idx="2"/>
+          <cx:dataPt idx="3"/>
+          <cx:dataPt idx="4"/>
+          <cx:dataPt idx="5"/>
+          <cx:dataPt idx="6"/>
+          <cx:dataPt idx="7"/>
+          <cx:dataPt idx="8"/>
+          <cx:dataPt idx="9"/>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:binning intervalClosed="r">
-              <cx:binCount val="10"/>
+              <cx:binCount val="12"/>
             </cx:binning>
           </cx:layoutPr>
         </cx:series>
@@ -705,15 +752,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>793750</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>457200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -749,8 +796,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3473450" y="800100"/>
-              <a:ext cx="3016250" cy="4851400"/>
+              <a:off x="4362450" y="457200"/>
+              <a:ext cx="7004050" cy="6692900"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1100,1074 +1147,1274 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FEEA0FC-F40E-B54F-9DE2-49C62AC28215}">
-  <dimension ref="B1:B177"/>
+  <dimension ref="A1:B176"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="12" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="B2" s="1">
         <f ca="1">RANDBETWEEN(2,10)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
       <c r="B3" s="1">
         <f t="shared" ref="B3:B6" ca="1" si="0">RANDBETWEEN(2,10)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
       <c r="B4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
       <c r="B5" s="1">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
       <c r="B6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="B7" s="1">
         <f ca="1">RANDBETWEEN(10,20)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="4"/>
       <c r="B8" s="1">
         <f t="shared" ref="B8:B16" ca="1" si="1">RANDBETWEEN(10,20)</f>
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
       <c r="B9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
       <c r="B10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
       <c r="B11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
       <c r="B12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
       <c r="B13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
       <c r="B14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
       <c r="B15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
       <c r="B16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="B17" s="1">
         <f ca="1">RANDBETWEEN(20,30)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
       <c r="B18" s="1">
         <f t="shared" ref="B18:B36" ca="1" si="2">RANDBETWEEN(20,30)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="4"/>
       <c r="B19" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="4"/>
       <c r="B20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
       <c r="B21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="4"/>
       <c r="B22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
       <c r="B23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="4"/>
       <c r="B24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="4"/>
       <c r="B25" s="1">
         <f t="shared" ca="1" si="2"/>
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="4"/>
       <c r="B26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="4"/>
       <c r="B27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="4"/>
       <c r="B28" s="1">
         <f t="shared" ca="1" si="2"/>
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="4"/>
       <c r="B29" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="4"/>
       <c r="B30" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="4"/>
       <c r="B31" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="4"/>
       <c r="B32" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="4"/>
       <c r="B33" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="4"/>
       <c r="B34" s="1">
         <f t="shared" ca="1" si="2"/>
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="4"/>
       <c r="B35" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="4"/>
       <c r="B36" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="B37" s="1">
         <f ca="1">RANDBETWEEN(30,40)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="4"/>
       <c r="B38" s="1">
         <f t="shared" ref="B38:B66" ca="1" si="3">RANDBETWEEN(30,40)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="4"/>
+      <c r="B39" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="4"/>
+      <c r="B40" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="4"/>
+      <c r="B41" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="4"/>
+      <c r="B42" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="4"/>
+      <c r="B43" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="4"/>
+      <c r="B44" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="4"/>
+      <c r="B45" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="4"/>
+      <c r="B46" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="4"/>
+      <c r="B47" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="4"/>
+      <c r="B48" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="4"/>
+      <c r="B49" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="4"/>
+      <c r="B50" s="1">
+        <f t="shared" ca="1" si="3"/>
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B39" s="1">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="4"/>
+      <c r="B51" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="4"/>
+      <c r="B52" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="4"/>
+      <c r="B53" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="4"/>
+      <c r="B54" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="4"/>
+      <c r="B55" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="4"/>
+      <c r="B56" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="4"/>
+      <c r="B57" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="4"/>
+      <c r="B58" s="1">
         <f t="shared" ca="1" si="3"/>
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B40" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B41" s="1">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="4"/>
+      <c r="B59" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="4"/>
+      <c r="B60" s="1">
         <f t="shared" ca="1" si="3"/>
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B42" s="1">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="4"/>
+      <c r="B61" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="4"/>
+      <c r="B62" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="4"/>
+      <c r="B63" s="1">
         <f t="shared" ca="1" si="3"/>
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B43" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B44" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B45" s="1">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="4"/>
+      <c r="B64" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="4"/>
+      <c r="B65" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="4"/>
+      <c r="B66" s="1">
         <f t="shared" ca="1" si="3"/>
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B46" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B47" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B48" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B56" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B57" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B58" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B59" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B60" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B66" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="B67" s="1">
         <f ca="1">RANDBETWEEN(40,50)</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="5"/>
       <c r="B68" s="1">
         <f t="shared" ref="B68:B112" ca="1" si="4">RANDBETWEEN(40,50)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="5"/>
+      <c r="B69" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="5"/>
+      <c r="B70" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="5"/>
+      <c r="B71" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="5"/>
+      <c r="B72" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="5"/>
+      <c r="B73" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="5"/>
+      <c r="B74" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="5"/>
+      <c r="B75" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="5"/>
+      <c r="B76" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="5"/>
+      <c r="B77" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="5"/>
+      <c r="B78" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="5"/>
+      <c r="B79" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="5"/>
+      <c r="B80" s="1">
+        <f t="shared" ca="1" si="4"/>
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B69" s="1">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="5"/>
+      <c r="B81" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="5"/>
+      <c r="B82" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="5"/>
+      <c r="B83" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="5"/>
+      <c r="B84" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="5"/>
+      <c r="B85" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="5"/>
+      <c r="B86" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="5"/>
+      <c r="B87" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="5"/>
+      <c r="B88" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="5"/>
+      <c r="B89" s="1">
         <f t="shared" ca="1" si="4"/>
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B70" s="1">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="5"/>
+      <c r="B90" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="5"/>
+      <c r="B91" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="5"/>
+      <c r="B92" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="5"/>
+      <c r="B93" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="5"/>
+      <c r="B94" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="5"/>
+      <c r="B95" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="5"/>
+      <c r="B96" s="1">
         <f t="shared" ca="1" si="4"/>
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B71" s="1">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="5"/>
+      <c r="B97" s="1">
         <f t="shared" ca="1" si="4"/>
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B72" s="1">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="5"/>
+      <c r="B98" s="1">
         <f t="shared" ca="1" si="4"/>
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B73" s="1">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="5"/>
+      <c r="B99" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="5"/>
+      <c r="B100" s="1">
         <f t="shared" ca="1" si="4"/>
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B74" s="1">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="5"/>
+      <c r="B101" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="5"/>
+      <c r="B102" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="5"/>
+      <c r="B103" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="5"/>
+      <c r="B104" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="5"/>
+      <c r="B105" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="5"/>
+      <c r="B106" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="5"/>
+      <c r="B107" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="5"/>
+      <c r="B108" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="5"/>
+      <c r="B109" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="5"/>
+      <c r="B110" s="1">
         <f t="shared" ca="1" si="4"/>
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B76" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B77" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B78" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B79" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B80" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B82" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B84" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B85" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B86" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B87" s="1">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="5"/>
+      <c r="B111" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" s="1">
         <f t="shared" ca="1" si="4"/>
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B88" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B89" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B90" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B91" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B92" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B93" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B94" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B95" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B96" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B97" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B98" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B99" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B100" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B101" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B102" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B103" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B104" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B105" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B106" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B107" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B108" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B109" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B110" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B111" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B112" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="4"/>
       <c r="B113" s="1">
         <f ca="1">RANDBETWEEN(50,60)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="4"/>
       <c r="B114" s="1">
         <f t="shared" ref="B114:B142" ca="1" si="5">RANDBETWEEN(50,60)</f>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="4"/>
       <c r="B115" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="4"/>
       <c r="B116" s="1">
         <f t="shared" ca="1" si="5"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="4"/>
+      <c r="B117" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="4"/>
+      <c r="B118" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="4"/>
+      <c r="B119" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="4"/>
+      <c r="B120" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="4"/>
+      <c r="B121" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="4"/>
+      <c r="B122" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="4"/>
+      <c r="B123" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B117" s="1">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="4"/>
+      <c r="B124" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="4"/>
+      <c r="B125" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="4"/>
+      <c r="B126" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="4"/>
+      <c r="B127" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="4"/>
+      <c r="B128" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="4"/>
+      <c r="B129" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="4"/>
+      <c r="B130" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="4"/>
+      <c r="B131" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="4"/>
+      <c r="B132" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="4"/>
+      <c r="B133" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="4"/>
+      <c r="B134" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="4"/>
+      <c r="B135" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="4"/>
+      <c r="B136" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="4"/>
+      <c r="B137" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="4"/>
+      <c r="B138" s="1">
         <f t="shared" ca="1" si="5"/>
         <v>56</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B118" s="1">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="4"/>
+      <c r="B139" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="4"/>
+      <c r="B140" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="4"/>
+      <c r="B141" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B142" s="1">
         <f t="shared" ca="1" si="5"/>
         <v>52</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B119" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B120" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B121" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B122" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B123" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B124" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B125" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B126" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B127" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B128" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B129" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B130" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B131" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B132" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B133" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B134" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B135" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B136" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B137" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B138" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B139" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B140" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B141" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B142" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="4"/>
       <c r="B143" s="1">
         <f ca="1">RANDBETWEEN(60,70)</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="4"/>
       <c r="B144" s="1">
         <f t="shared" ref="B144:B162" ca="1" si="6">RANDBETWEEN(60,70)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="4"/>
       <c r="B145" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="4"/>
       <c r="B146" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="4"/>
       <c r="B147" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="4"/>
       <c r="B148" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="4"/>
       <c r="B149" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="4"/>
       <c r="B150" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="4"/>
       <c r="B151" s="1">
         <f t="shared" ca="1" si="6"/>
         <v>67</v>
       </c>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="4"/>
       <c r="B152" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="4"/>
       <c r="B153" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="4"/>
       <c r="B154" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="4"/>
       <c r="B155" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="4"/>
       <c r="B156" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="4"/>
       <c r="B157" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="4"/>
       <c r="B158" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="4"/>
       <c r="B159" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="4"/>
       <c r="B160" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="4"/>
       <c r="B161" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="B162" s="1">
-        <f t="shared" ca="1" si="6"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+        <f ca="1">RANDBETWEEN(70,80)</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="4"/>
       <c r="B163" s="1">
-        <f ca="1">RANDBETWEEN(70,80)</f>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+        <f t="shared" ref="B163:B171" ca="1" si="7">RANDBETWEEN(70,80)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="4"/>
       <c r="B164" s="1">
-        <f t="shared" ref="B164:B172" ca="1" si="7">RANDBETWEEN(70,80)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+        <f t="shared" ca="1" si="7"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="4"/>
       <c r="B165" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="4"/>
       <c r="B166" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="4"/>
       <c r="B167" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="4"/>
       <c r="B168" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="4"/>
       <c r="B169" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="4"/>
       <c r="B170" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="4"/>
       <c r="B171" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="B172" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+        <f ca="1">RANDBETWEEN(80,90)</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="5"/>
       <c r="B173" s="1">
         <f ca="1">RANDBETWEEN(80,90)</f>
-        <v>89</v>
-      </c>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="5"/>
       <c r="B174" s="1">
         <f t="shared" ref="B174:B177" ca="1" si="8">RANDBETWEEN(80,90)</f>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="5"/>
       <c r="B175" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="5"/>
       <c r="B176" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>88</v>
-      </c>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B177" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A67:A111"/>
+    <mergeCell ref="A112:A141"/>
+    <mergeCell ref="A142:A161"/>
+    <mergeCell ref="A162:A171"/>
+    <mergeCell ref="A172:A176"/>
+    <mergeCell ref="A7:A16"/>
+    <mergeCell ref="A17:A36"/>
+    <mergeCell ref="A37:A66"/>
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
